--- a/product_selector_out/STM32F469-479 - diff.xlsx
+++ b/product_selector_out/STM32F469-479 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$126</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E156"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1894</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="18">
@@ -713,22 +713,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -740,29 +736,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32F479ZG</t>
+          <t>STM32F469BG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -772,116 +764,112 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>106 (workbook and API agree)</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32F479ZG</t>
+          <t>STM32F469BG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32F479ZG</t>
+          <t>STM32F469BG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>159 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32F479ZG</t>
+          <t>STM32F469BG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>4 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32F479ZG</t>
+          <t>STM32F469BG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -893,18 +881,18 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32F479ZG</t>
+          <t>STM32F469AG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -916,34 +904,30 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32F469BG</t>
+          <t>STM32F469AG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32F469BG</t>
+          <t>STM32F469NG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -961,16 +945,16 @@
           <t>161</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32F469BG</t>
+          <t>STM32F469NG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -980,7 +964,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>159 (workbook and API agree)</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -988,50 +972,54 @@
           <t>161</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32F469BG</t>
+          <t>STM32F469NG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>159 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32F469BG</t>
+          <t>STM32F469NG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1043,18 +1031,18 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32F469AG</t>
+          <t>STM32F469NG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1066,18 +1054,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32F469AG</t>
+          <t>STM32F469II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1089,88 +1077,76 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32F469NG</t>
+          <t>STM32F469II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32F469NG</t>
+          <t>STM32F479VG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32F469NG</t>
+          <t>STM32F479VG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>159 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32F469NG</t>
+          <t>STM32F469AI</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1193,7 +1169,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32F469NG</t>
+          <t>STM32F469AI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1216,87 +1192,99 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32F469II</t>
+          <t>STM32F469NI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32F469II</t>
+          <t>STM32F469NI</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32F479VG</t>
+          <t>STM32F469NI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>159 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32F479VG</t>
+          <t>STM32F469NI</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -1308,18 +1296,18 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32F469AI</t>
+          <t>STM32F469NI</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -1331,150 +1319,162 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32F469AI</t>
+          <t>STM32F469ZE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>LQFP 144 20x20x1.4 mm</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>LQPF144</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32F469NI</t>
+          <t>STM32F469ZE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>LQFP 144 20x20x1.4 mm</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>LQPF144</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32F469NI</t>
+          <t>STM32F469ZE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>LQFP 144 20x20x1.4 mm (workbook and API agree)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>LQPF144</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32F469NI</t>
+          <t>STM32F469ZE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>159 (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32F469NI</t>
+          <t>STM32F469ZE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32F469NI</t>
+          <t>STM32F469ZE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1486,22 +1486,18 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>LQFP 144 20x20x1.4 mm</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LQPF144</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1513,137 +1509,117 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>LQFP 144 20x20x1.4 mm</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LQPF144</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32F469ZE</t>
+          <t>STM32F469ZG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>LQFP 144 20x20x1.4 mm (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LQPF144</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32F469ZE</t>
+          <t>STM32F469ZG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32F469ZE</t>
+          <t>STM32F469VG</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32F469ZE</t>
+          <t>STM32F469VG</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>4 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32F469ZE</t>
+          <t>STM32F479NG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1666,7 +1642,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32F469ZE</t>
+          <t>STM32F479NG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1689,169 +1665,145 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F469VI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>LQFP 144 20x20x1.4 mm</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LQPF144</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F469VI</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>LQFP 144 20x20x1.4 mm</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LQPF144</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F469ZI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>LQFP 144 20x20x1.4 mm (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LQPF144</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F469ZI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F469VE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F469VE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>4 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F479VI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1874,7 +1826,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F479VI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1897,134 +1849,134 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32F469VG</t>
+          <t>STM32F469AE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>UFBGA 169 7x7x0.6 P 0.5 mm</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>UFBGA169, WLCSP168</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32F469VG</t>
+          <t>STM32F469AE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>UFBGA 169 7x7x0.6 P 0.5 mm</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>UFBGA169, WLCSP168</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32F479NG</t>
+          <t>STM32F469AE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>UFBGA 169 7x7x0.6 P 0.5 mm (workbook and API agree)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>UFBGA169, WLCSP168</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32F479NG</t>
+          <t>STM32F469AE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32F479NG</t>
+          <t>STM32F469AE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>159 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32F479NG</t>
+          <t>STM32F479ZI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2047,7 +1999,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32F479NG</t>
+          <t>STM32F479ZI</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2070,7 +2022,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32F469VI</t>
+          <t>STM32F479NI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2093,7 +2045,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32F469VI</t>
+          <t>STM32F479NI</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2116,7 +2068,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479IG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2126,12 +2078,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LQFP 144 20x20x1.4 mm</t>
+          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LQPF144</t>
+          <t>LQFP176, UFBGA176</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
@@ -2143,7 +2095,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479IG</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2153,12 +2105,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LQFP 144 20x20x1.4 mm</t>
+          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LQPF144</t>
+          <t>LQFP176, UFBGA176</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -2170,7 +2122,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479IG</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2180,12 +2132,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LQFP 144 20x20x1.4 mm (workbook and API agree)</t>
+          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm (workbook and API agree)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LQPF144</t>
+          <t>LQFP176, UFBGA176</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2197,134 +2149,134 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479IG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479IG</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479BG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>4 (workbook and API agree)</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479BG</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479BG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>159 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32F469VE</t>
+          <t>STM32F479BG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2347,7 +2299,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32F469VE</t>
+          <t>STM32F479BG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2370,53 +2322,61 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32F479VI</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>UFBGA 169 7x7x0.6 P 0.5 mm</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>UFBGA169, WLCSP168</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32F479VI</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>UFBGA 169 7x7x0.6 P 0.5 mm</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>UFBGA169, WLCSP168</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32F469AE</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2426,7 +2386,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>UFBGA 169 7x7x0.6 P 0.5 mm</t>
+          <t>UFBGA 169 7x7x0.6 P 0.5 mm (workbook and API agree)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2434,104 +2394,108 @@
           <t>UFBGA169, WLCSP168</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32F469AE</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>UFBGA 169 7x7x0.6 P 0.5 mm</t>
+          <t>128</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>UFBGA169, WLCSP168</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32F469AE</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>UFBGA 169 7x7x0.6 P 0.5 mm (workbook and API agree)</t>
+          <t>128</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>UFBGA169, WLCSP168</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32F469AE</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>128 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32F469AE</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -2543,34 +2507,30 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F469NE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2580,24 +2540,24 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F469NE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2607,105 +2567,97 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>106 (workbook and API agree)</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F469NE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>159 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F469NE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F469NE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>4 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F479II</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2728,7 +2680,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F479II</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2751,7 +2703,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32F479NI</t>
+          <t>STM32F479BI</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2778,7 +2730,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32F479NI</t>
+          <t>STM32F479BI</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2805,7 +2757,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32F479NI</t>
+          <t>STM32F479BI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2832,7 +2784,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32F479NI</t>
+          <t>STM32F479BI</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2855,7 +2807,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32F479NI</t>
+          <t>STM32F479BI</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2878,22 +2830,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32F479IG</t>
+          <t>STM32F479AI</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm</t>
+          <t>128</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LQFP176, UFBGA176</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -2905,22 +2857,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32F479IG</t>
+          <t>STM32F479AI</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm</t>
+          <t>128</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LQFP176, UFBGA176</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -2932,22 +2884,22 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32F479IG</t>
+          <t>STM32F479AI</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm (workbook and API agree)</t>
+          <t>128 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LQFP176, UFBGA176</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -2959,7 +2911,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32F479IG</t>
+          <t>STM32F479AI</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2982,7 +2934,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32F479IG</t>
+          <t>STM32F479AI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3005,22 +2957,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32F479BG</t>
+          <t>STM32F469IE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>LQFP176, UFBGA176</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -3032,22 +2984,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32F479BG</t>
+          <t>STM32F469IE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>LQFP176, UFBGA176</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -3059,22 +3011,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32F479BG</t>
+          <t>STM32F469IE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>159 (workbook and API agree)</t>
+          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm (workbook and API agree)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>LQFP176, UFBGA176</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
@@ -3086,7 +3038,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32F479BG</t>
+          <t>STM32F469IE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3109,7 +3061,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32F479BG</t>
+          <t>STM32F469IE</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3132,22 +3084,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32F479AG</t>
+          <t>STM32F469BE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>UFBGA 169 7x7x0.6 P 0.5 mm</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>UFBGA169, WLCSP168</t>
+          <t>161</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -3159,22 +3111,22 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32F479AG</t>
+          <t>STM32F469BE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>UFBGA 169 7x7x0.6 P 0.5 mm</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>UFBGA169, WLCSP168</t>
+          <t>161</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -3186,22 +3138,22 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32F479AG</t>
+          <t>STM32F469BE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>UFBGA 169 7x7x0.6 P 0.5 mm (workbook and API agree)</t>
+          <t>159 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>UFBGA169, WLCSP168</t>
+          <t>161</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -3213,61 +3165,53 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32F479AG</t>
+          <t>STM32F469BE</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32F479AG</t>
+          <t>STM32F469BE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32F479AG</t>
+          <t>STM32F469BI</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3277,876 +3221,122 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>128 (workbook and API agree)</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32F479AG</t>
+          <t>STM32F469BI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32F479AG</t>
+          <t>STM32F469BI</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>159 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32F469NE</t>
+          <t>STM32F469BI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32F469NE</t>
+          <t>STM32F469BI</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E126" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>STM32F469NE</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>159 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>STM32F469NE</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>STM32F469NE</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr">
-        <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E129" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>STM32F479II</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>STM32F479II</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>STM32F479BI</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>STM32F479BI</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E133" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>STM32F479BI</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>159 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E134" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>STM32F479BI</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>STM32F479BI</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>STM32F479AI</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>STM32F479AI</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E138" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>STM32F479AI</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>128 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="E139" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>STM32F479AI</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>STM32F479AI</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E141" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>STM32F469IE</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>LQFP176, UFBGA176</t>
-        </is>
-      </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>STM32F469IE</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>LQFP176, UFBGA176</t>
-        </is>
-      </c>
-      <c r="E143" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>STM32F469IE</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>UFBGA 176+25 10x10x0.6 P 0.65 mm (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>LQFP176, UFBGA176</t>
-        </is>
-      </c>
-      <c r="E144" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>STM32F469IE</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E145" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>STM32F469IE</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>STM32F469BE</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>STM32F469BE</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E148" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>STM32F469BE</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>159 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E149" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>STM32F469BE</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>STM32F469BE</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E151" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>STM32F469BI</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>STM32F469BI</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E153" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>STM32F469BI</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>159 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="E154" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>STM32F469BI</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E155" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>STM32F469BI</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E156" s="3" t="inlineStr">
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E156"/>
+  <autoFilter ref="A18:E126"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32F469-479 - diff.xlsx
+++ b/product_selector_out/STM32F469-479 - diff.xlsx
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1980</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1904</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="18">
